--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>69.7844999619951</v>
+        <v>11.3399812438242</v>
       </c>
       <c r="D2" t="n">
-        <v>69.00707518354245</v>
+        <v>11.21364971732565</v>
       </c>
       <c r="E2" t="n">
-        <v>5.914577634966181</v>
+        <v>0.9611188656820044</v>
       </c>
       <c r="F2" t="n">
-        <v>6.17108439953753</v>
+        <v>1.002801214924849</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.80879944184426</v>
+        <v>10.85642990929969</v>
       </c>
       <c r="D3" t="n">
-        <v>65.433959074995</v>
+        <v>10.63301834968669</v>
       </c>
       <c r="E3" t="n">
-        <v>5.914577634966181</v>
+        <v>0.9611188656820044</v>
       </c>
       <c r="F3" t="n">
-        <v>6.17108439953753</v>
+        <v>1.002801214924849</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>65.58384232582439</v>
+        <v>10.65737437794646</v>
       </c>
       <c r="D4" t="n">
-        <v>64.24428008488383</v>
+        <v>10.43969551379362</v>
       </c>
       <c r="E4" t="n">
-        <v>5.914577634966181</v>
+        <v>0.9611188656820044</v>
       </c>
       <c r="F4" t="n">
-        <v>6.17108439953753</v>
+        <v>1.002801214924849</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>73.15591387232033</v>
+        <v>11.88783600425205</v>
       </c>
       <c r="D5" t="n">
-        <v>74.46248902751199</v>
+        <v>12.1001544669707</v>
       </c>
       <c r="E5" t="n">
-        <v>5.914577634966181</v>
+        <v>0.9611188656820044</v>
       </c>
       <c r="F5" t="n">
-        <v>6.17108439953753</v>
+        <v>1.002801214924849</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>69.42106340904434</v>
+        <v>11.28092280396971</v>
       </c>
       <c r="D6" t="n">
-        <v>70.84046026943885</v>
+        <v>11.51157479378381</v>
       </c>
       <c r="E6" t="n">
-        <v>5.914577634966181</v>
+        <v>0.9611188656820044</v>
       </c>
       <c r="F6" t="n">
-        <v>6.17108439953753</v>
+        <v>1.002801214924849</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>70.66708447921725</v>
+        <v>11.4834012278728</v>
       </c>
       <c r="D7" t="n">
-        <v>69.93149724306713</v>
+        <v>11.36386830199841</v>
       </c>
       <c r="E7" t="n">
-        <v>5.914577634966181</v>
+        <v>0.9611188656820044</v>
       </c>
       <c r="F7" t="n">
-        <v>6.17108439953753</v>
+        <v>1.002801214924849</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>53.84996713310427</v>
+        <v>8.750619659129445</v>
       </c>
       <c r="D8" t="n">
-        <v>53.6551422675611</v>
+        <v>8.718960618478679</v>
       </c>
       <c r="E8" t="n">
-        <v>5.914577634966181</v>
+        <v>0.9611188656820044</v>
       </c>
       <c r="F8" t="n">
-        <v>6.17108439953753</v>
+        <v>1.002801214924849</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>60.28214300671179</v>
+        <v>9.795848238590667</v>
       </c>
       <c r="D9" t="n">
-        <v>60.58520079659388</v>
+        <v>9.845095129446506</v>
       </c>
       <c r="E9" t="n">
-        <v>5.914577634966181</v>
+        <v>0.9611188656820044</v>
       </c>
       <c r="F9" t="n">
-        <v>6.17108439953753</v>
+        <v>1.002801214924849</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
